--- a/meta/TD2_Kutuphane.xlsx
+++ b/meta/TD2_Kutuphane.xlsx
@@ -41,7 +41,7 @@
     <t xml:space="preserve">The Division 2 — eşya kütüphanesi</t>
   </si>
   <si>
-    <t xml:space="preserve">TD2 Loot Advisor kütüphane sürümü 2026-10-25.4 · Son sezon: Y8S3 Red Horizon</t>
+    <t xml:space="preserve">TD2 Loot Advisor kütüphane sürümü 2026-10-25.5 · Son sezon: Y8S3 Red Horizon</t>
   </si>
   <si>
     <t xml:space="preserve">Bölüm</t>
